--- a/figures/FigS16_sensitivity_combined.xlsx
+++ b/figures/FigS16_sensitivity_combined.xlsx
@@ -1120,34 +1120,34 @@
         <v>197.934651517</v>
       </c>
       <c r="C2" t="n">
-        <v>119.3570443625937</v>
+        <v>315.7556046722105</v>
       </c>
       <c r="D2" t="n">
-        <v>288.9451745084062</v>
+        <v>92.54659519878948</v>
       </c>
       <c r="E2" t="n">
-        <v>265.5839051773746</v>
+        <v>306.7291159386752</v>
       </c>
       <c r="F2" t="n">
-        <v>274.1556162586256</v>
+        <v>233.010425437325</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-1.734380362699916e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-1.061982786730941e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>606.2368703879999</v>
+        <v>606.236851388</v>
       </c>
       <c r="J2" t="n">
-        <v>591.36027029</v>
+        <v>591.36024059</v>
       </c>
       <c r="K2" t="n">
-        <v>1145.976391824</v>
+        <v>1145.976392764</v>
       </c>
       <c r="L2" t="n">
-        <v>1145.976391824</v>
+        <v>1145.976391019</v>
       </c>
     </row>
     <row r="3">
@@ -1160,34 +1160,34 @@
         <v>286.108775997</v>
       </c>
       <c r="C3" t="n">
-        <v>393.8537433124421</v>
+        <v>406.1638697993921</v>
       </c>
       <c r="D3" t="n">
-        <v>126.4004497285579</v>
+        <v>114.0902702416079</v>
       </c>
       <c r="E3" t="n">
-        <v>211.1831765288802</v>
+        <v>192.6469019652164</v>
       </c>
       <c r="F3" t="n">
-        <v>128.4302466321199</v>
+        <v>146.9665728557836</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3.200000264769187e-07</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>806.3629690380001</v>
+        <v>806.362916038</v>
       </c>
       <c r="J3" t="n">
-        <v>769.939591909</v>
+        <v>769.939518209</v>
       </c>
       <c r="K3" t="n">
-        <v>1145.976392199</v>
+        <v>1145.976390859</v>
       </c>
       <c r="L3" t="n">
-        <v>1145.976392199</v>
+        <v>1145.976391179</v>
       </c>
     </row>
     <row r="4">
@@ -1200,34 +1200,34 @@
         <v>66.103131995</v>
       </c>
       <c r="C4" t="n">
-        <v>12.4174931242046</v>
+        <v>97.53969400078617</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3551906767954</v>
+        <v>29.23296180021383</v>
       </c>
       <c r="E4" t="n">
-        <v>228.3036976289532</v>
+        <v>361.7540150283517</v>
       </c>
       <c r="F4" t="n">
-        <v>404.9764113940467</v>
+        <v>271.5261219946482</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>318.7310952419066</v>
       </c>
       <c r="H4" t="n">
-        <v>319.8204627000002</v>
+        <v>1.089370598093637</v>
       </c>
       <c r="I4" t="n">
-        <v>192.875815796</v>
+        <v>192.875787796</v>
       </c>
       <c r="J4" t="n">
-        <v>273.351655078</v>
+        <v>273.351644098</v>
       </c>
       <c r="K4" t="n">
         <v>826.1559248189999</v>
       </c>
       <c r="L4" t="n">
-        <v>1145.976387519</v>
+        <v>1145.976390659</v>
       </c>
     </row>
     <row r="5">
@@ -1240,34 +1240,34 @@
         <v>199.369597723</v>
       </c>
       <c r="C5" t="n">
-        <v>116.5041217308391</v>
+        <v>307.8877890951763</v>
       </c>
       <c r="D5" t="n">
-        <v>290.3631509341609</v>
+        <v>98.97945256982376</v>
       </c>
       <c r="E5" t="n">
-        <v>272.5657835950247</v>
+        <v>312.6282717825494</v>
       </c>
       <c r="F5" t="n">
-        <v>284.4307297269754</v>
+        <v>244.3682720594506</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-2.249653071492019e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1.534707683507048e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>606.2368703879999</v>
+        <v>606.236839388</v>
       </c>
       <c r="J5" t="n">
-        <v>599.2385227359999</v>
+        <v>599.238489556</v>
       </c>
       <c r="K5" t="n">
-        <v>1163.23338371</v>
+        <v>1163.23338323</v>
       </c>
       <c r="L5" t="n">
-        <v>1163.23338371</v>
+        <v>1163.233380965</v>
       </c>
     </row>
     <row r="6">
@@ -1280,34 +1280,34 @@
         <v>199.173144423</v>
       </c>
       <c r="C6" t="n">
-        <v>116.2397044852711</v>
+        <v>307.7400948572428</v>
       </c>
       <c r="D6" t="n">
-        <v>290.8240214797288</v>
+        <v>99.32360010775722</v>
       </c>
       <c r="E6" t="n">
-        <v>273.0723056875814</v>
+        <v>312.9695075423074</v>
       </c>
       <c r="F6" t="n">
-        <v>285.0519675574187</v>
+        <v>245.1547962226924</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-1.653730743183485e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-1.12689291737407e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>606.2368703879999</v>
+        <v>606.236839388</v>
       </c>
       <c r="J6" t="n">
-        <v>599.6145071890001</v>
+        <v>599.614427869</v>
       </c>
       <c r="K6" t="n">
-        <v>1164.361143633</v>
+        <v>1164.361143153</v>
       </c>
       <c r="L6" t="n">
-        <v>1164.361143633</v>
+        <v>1164.361141488</v>
       </c>
     </row>
     <row r="7">
@@ -1320,34 +1320,34 @@
         <v>64.3856949585</v>
       </c>
       <c r="C7" t="n">
-        <v>139.5148662738756</v>
+        <v>203.3405351764819</v>
       </c>
       <c r="D7" t="n">
-        <v>82.59353707062439</v>
+        <v>18.76786816801811</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.61759926788733e-07</v>
+        <v>-9.865109144236211e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.177400732445618e-07</v>
+        <v>-7.084887817320979e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.680979061568158e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.702048664976437e-09</v>
       </c>
       <c r="I7" t="n">
         <v>286.494098303</v>
       </c>
       <c r="J7" t="n">
-        <v>169.1582138613</v>
+        <v>169.1581729213</v>
       </c>
       <c r="K7" t="n">
-        <v>286.4940980235</v>
+        <v>286.4940981335</v>
       </c>
       <c r="L7" t="n">
-        <v>286.4940980235</v>
+        <v>286.4940984033</v>
       </c>
     </row>
     <row r="8">
@@ -1360,34 +1360,34 @@
         <v>117.603306808</v>
       </c>
       <c r="C8" t="n">
-        <v>245.4932945569572</v>
+        <v>395.348983264098</v>
       </c>
       <c r="D8" t="n">
-        <v>209.8915943230428</v>
+        <v>60.03590561590198</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.93315329595718e-07</v>
+        <v>-3.072358340128284e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.646846466877451e-07</v>
+        <v>-2.307641607634997e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-3.92430069639943e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-2.569959489789879e-09</v>
       </c>
       <c r="I8" t="n">
         <v>572.988195688</v>
       </c>
       <c r="J8" t="n">
-        <v>322.973945531</v>
+        <v>322.973917861</v>
       </c>
       <c r="K8" t="n">
-        <v>572.98819503</v>
+        <v>572.98819515</v>
       </c>
       <c r="L8" t="n">
-        <v>572.98819503</v>
+        <v>572.988194755</v>
       </c>
     </row>
     <row r="9">
@@ -1400,34 +1400,34 @@
         <v>182.314777496</v>
       </c>
       <c r="C9" t="n">
-        <v>115.2640734350201</v>
+        <v>305.4094649405625</v>
       </c>
       <c r="D9" t="n">
-        <v>278.3162461459798</v>
+        <v>88.1707816404375</v>
       </c>
       <c r="E9" t="n">
-        <v>282.2114625154956</v>
+        <v>318.3833352211351</v>
       </c>
       <c r="F9" t="n">
-        <v>287.8698326315044</v>
+        <v>251.6980334758649</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-1.734344737345506e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-1.065522584804373e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>575.8950970769999</v>
+        <v>575.895024077</v>
       </c>
       <c r="J9" t="n">
-        <v>591.36027029</v>
+        <v>591.3601874399999</v>
       </c>
       <c r="K9" t="n">
-        <v>1145.976392224</v>
+        <v>1145.976392774</v>
       </c>
       <c r="L9" t="n">
-        <v>1145.976392224</v>
+        <v>1145.976391029</v>
       </c>
     </row>
     <row r="10">
@@ -1440,34 +1440,34 @@
         <v>189.740315566</v>
       </c>
       <c r="C10" t="n">
-        <v>123.5938592061186</v>
+        <v>326.3665461070375</v>
       </c>
       <c r="D10" t="n">
-        <v>298.4293190048813</v>
+        <v>95.65661610396239</v>
       </c>
       <c r="E10" t="n">
-        <v>272.3289356750724</v>
+        <v>305.5005550896393</v>
       </c>
       <c r="F10" t="n">
-        <v>261.8839627719276</v>
+        <v>228.7123599073608</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-1.744319398983739e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.068068582947913e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>611.7634937769999</v>
+        <v>611.7634777769999</v>
       </c>
       <c r="J10" t="n">
-        <v>591.36027029</v>
+        <v>591.3601874399999</v>
       </c>
       <c r="K10" t="n">
-        <v>1145.976392224</v>
+        <v>1145.976392774</v>
       </c>
       <c r="L10" t="n">
-        <v>1145.976392224</v>
+        <v>1145.976391019</v>
       </c>
     </row>
     <row r="11">
@@ -1480,34 +1480,34 @@
         <v>196.034940376</v>
       </c>
       <c r="C11" t="n">
-        <v>113.8014502588842</v>
+        <v>301.0584391120578</v>
       </c>
       <c r="D11" t="n">
-        <v>275.4959297121158</v>
+        <v>88.23891985894221</v>
       </c>
       <c r="E11" t="n">
-        <v>264.7720290469903</v>
+        <v>315.9016586248499</v>
       </c>
       <c r="F11" t="n">
-        <v>295.8720424300098</v>
+        <v>244.7424341921502</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-1.138031857952993e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-6.968311391718675e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>585.3323203469999</v>
+        <v>585.332299347</v>
       </c>
       <c r="J11" t="n">
-        <v>591.36027029</v>
+        <v>591.3601874399999</v>
       </c>
       <c r="K11" t="n">
-        <v>1145.976391824</v>
+        <v>1145.976392164</v>
       </c>
       <c r="L11" t="n">
-        <v>1145.976391824</v>
+        <v>1145.976391019</v>
       </c>
     </row>
     <row r="12">
@@ -1520,34 +1520,34 @@
         <v>194.768466284</v>
       </c>
       <c r="C12" t="n">
-        <v>110.2578973721883</v>
+        <v>289.137280950239</v>
       </c>
       <c r="D12" t="n">
-        <v>263.6242777988116</v>
+        <v>84.74488022076093</v>
       </c>
       <c r="E12" t="n">
-        <v>262.3522861771566</v>
+        <v>322.5520074883331</v>
       </c>
       <c r="F12" t="n">
-        <v>314.9734646918435</v>
+        <v>254.7737570206669</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-9.392488723774118e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-5.751138310678881e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>568.6506414549999</v>
+        <v>568.6506274549999</v>
       </c>
       <c r="J12" t="n">
-        <v>591.36027029</v>
+        <v>591.3601874399999</v>
       </c>
       <c r="K12" t="n">
-        <v>1145.976392324</v>
+        <v>1145.976391964</v>
       </c>
       <c r="L12" t="n">
-        <v>1145.976392324</v>
+        <v>1145.976391019</v>
       </c>
     </row>
     <row r="13">
@@ -1560,34 +1560,34 @@
         <v>170.540365174</v>
       </c>
       <c r="C13" t="n">
-        <v>84.83786931423465</v>
+        <v>221.5309994765753</v>
       </c>
       <c r="D13" t="n">
-        <v>200.7951986667653</v>
+        <v>64.10205450442467</v>
       </c>
       <c r="E13" t="n">
-        <v>292.5076205502558</v>
+        <v>356.5041184428651</v>
       </c>
       <c r="F13" t="n">
-        <v>397.2953387187443</v>
+        <v>333.2988552761348</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-1.744215607269918e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-1.078425016962492e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>456.173433155</v>
+        <v>456.173419155</v>
       </c>
       <c r="J13" t="n">
-        <v>591.36027029</v>
+        <v>591.3601874399999</v>
       </c>
       <c r="K13" t="n">
-        <v>1145.976392424</v>
+        <v>1145.976392874</v>
       </c>
       <c r="L13" t="n">
-        <v>1145.976392424</v>
+        <v>1145.976391119</v>
       </c>
     </row>
     <row r="14">
@@ -1600,34 +1600,34 @@
         <v>146.3146013328</v>
       </c>
       <c r="C14" t="n">
-        <v>64.31699211280279</v>
+        <v>166.6046382324538</v>
       </c>
       <c r="D14" t="n">
-        <v>149.8882374281972</v>
+        <v>47.60055130854622</v>
       </c>
       <c r="E14" t="n">
-        <v>265.6627070197884</v>
+        <v>354.2684412060042</v>
       </c>
       <c r="F14" t="n">
-        <v>519.7938542204118</v>
+        <v>431.1881601241959</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1.038541228283305e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-6.459089106771465e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>360.5198308737999</v>
+        <v>360.5197908738</v>
       </c>
       <c r="J14" t="n">
-        <v>591.36027029</v>
+        <v>591.3601874399999</v>
       </c>
       <c r="K14" t="n">
-        <v>1145.976392114</v>
+        <v>1145.976392204</v>
       </c>
       <c r="L14" t="n">
-        <v>1145.976392114</v>
+        <v>1145.976391159</v>
       </c>
     </row>
     <row r="15">
@@ -1640,34 +1640,34 @@
         <v>158.923768248</v>
       </c>
       <c r="C15" t="n">
-        <v>29.74566198967751</v>
+        <v>109.0747704510046</v>
       </c>
       <c r="D15" t="n">
-        <v>167.4917444413225</v>
+        <v>88.16261097999543</v>
       </c>
       <c r="E15" t="n">
-        <v>269.3151012529731</v>
+        <v>433.7391611944537</v>
       </c>
       <c r="F15" t="n">
-        <v>412.0064737450268</v>
+        <v>247.5824388035462</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>108.1402921452776</v>
       </c>
       <c r="H15" t="n">
-        <v>108.4936422800001</v>
+        <v>0.3533518797224957</v>
       </c>
       <c r="I15" t="n">
-        <v>356.161174679</v>
+        <v>356.161149679</v>
       </c>
       <c r="J15" t="n">
-        <v>479.948441862</v>
+        <v>479.948397132</v>
       </c>
       <c r="K15" t="n">
         <v>1037.482749677</v>
       </c>
       <c r="L15" t="n">
-        <v>1145.976391957</v>
+        <v>1145.976393702</v>
       </c>
     </row>
     <row r="16">
@@ -1680,34 +1680,34 @@
         <v>116.3189623694</v>
       </c>
       <c r="C16" t="n">
-        <v>23.29745700935933</v>
+        <v>24.32162067993158</v>
       </c>
       <c r="D16" t="n">
-        <v>64.75653845164067</v>
+        <v>63.73233858106843</v>
       </c>
       <c r="E16" t="n">
-        <v>205.2815504977743</v>
+        <v>209.3852147564464</v>
       </c>
       <c r="F16" t="n">
-        <v>128.5973899322258</v>
+        <v>124.4937618735536</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>606.8525829630718</v>
       </c>
       <c r="H16" t="n">
-        <v>496.8687544128999</v>
+        <v>0.8719110378283403</v>
       </c>
       <c r="I16" t="n">
-        <v>204.3729578304</v>
+        <v>204.3729216304</v>
       </c>
       <c r="J16" t="n">
-        <v>334.6048091154</v>
+        <v>334.6047921004</v>
       </c>
       <c r="K16" t="n">
         <v>538.2518982604</v>
       </c>
       <c r="L16" t="n">
-        <v>1035.1206526733</v>
+        <v>1145.9763922613</v>
       </c>
     </row>
     <row r="17">
@@ -1720,34 +1720,34 @@
         <v>229.626520317</v>
       </c>
       <c r="C17" t="n">
-        <v>231.7957655438288</v>
+        <v>410.997298531326</v>
       </c>
       <c r="D17" t="n">
-        <v>297.959282127171</v>
+        <v>118.7576961396738</v>
       </c>
       <c r="E17" t="n">
-        <v>221.5693024542014</v>
+        <v>219.3293103506404</v>
       </c>
       <c r="F17" t="n">
-        <v>165.0255206767987</v>
+        <v>167.2655670203595</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-1.628747882063861e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1.1252054678381e-08</v>
       </c>
       <c r="I17" t="n">
-        <v>759.3815679879999</v>
+        <v>759.3815149879999</v>
       </c>
       <c r="J17" t="n">
-        <v>638.7249852689999</v>
+        <v>638.7249626190001</v>
       </c>
       <c r="K17" t="n">
-        <v>1145.976391119</v>
+        <v>1145.976392359</v>
       </c>
       <c r="L17" t="n">
-        <v>1145.976391119</v>
+        <v>1145.976390719</v>
       </c>
     </row>
     <row r="18">
@@ -1760,34 +1760,34 @@
         <v>200.211127467</v>
       </c>
       <c r="C18" t="n">
-        <v>121.0439288840652</v>
+        <v>317.920810032773</v>
       </c>
       <c r="D18" t="n">
-        <v>290.0580946269348</v>
+        <v>93.18120747822701</v>
       </c>
       <c r="E18" t="n">
-        <v>263.0089486059436</v>
+        <v>303.8443031930732</v>
       </c>
       <c r="F18" t="n">
-        <v>271.6542914300564</v>
+        <v>230.8189430829268</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-2.335627381472544e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.43727774401909e-09</v>
       </c>
       <c r="I18" t="n">
-        <v>611.313150978</v>
+        <v>611.313144978</v>
       </c>
       <c r="J18" t="n">
-        <v>593.63674624</v>
+        <v>593.63674565</v>
       </c>
       <c r="K18" t="n">
-        <v>1145.976391014</v>
+        <v>1145.976391254</v>
       </c>
       <c r="L18" t="n">
-        <v>1145.976391014</v>
+        <v>1145.976391019</v>
       </c>
     </row>
     <row r="19">
@@ -1800,34 +1800,34 @@
         <v>231.598730847</v>
       </c>
       <c r="C19" t="n">
-        <v>308.7848168178661</v>
+        <v>422.5357156021011</v>
       </c>
       <c r="D19" t="n">
-        <v>234.4921328631338</v>
+        <v>120.741230878899</v>
       </c>
       <c r="E19" t="n">
-        <v>229.0214402040726</v>
+        <v>210.9157646171492</v>
       </c>
       <c r="F19" t="n">
-        <v>142.0792688319273</v>
+        <v>160.1849500888509</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-5.012264078706813e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-3.773708520193311e-09</v>
       </c>
       <c r="I19" t="n">
-        <v>774.875680528</v>
+        <v>774.8756773280001</v>
       </c>
       <c r="J19" t="n">
-        <v>672.4141481040001</v>
+        <v>672.414106214</v>
       </c>
       <c r="K19" t="n">
-        <v>1145.976389564</v>
+        <v>1145.976392034</v>
       </c>
       <c r="L19" t="n">
-        <v>1145.976389564</v>
+        <v>1145.976391529</v>
       </c>
     </row>
   </sheetData>
